--- a/01-Projects/하루보고 홍보/업무 일정관리 양식 (무료배포).xlsx
+++ b/01-Projects/하루보고 홍보/업무 일정관리 양식 (무료배포).xlsx
@@ -113,41 +113,49 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BFDBFE"/>
+        <bgColor rgb="00BFDBFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7F0FE"/>
+        <bgColor rgb="00E7F0FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="003182F6"/>
+        <bgColor rgb="003182F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00A5D6A7"/>
+        <bgColor rgb="00A5D6A7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF4E5"/>
+        <bgColor rgb="00FFF4E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5B971"/>
+        <bgColor rgb="00F5B971"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FDE7E9"/>
+        <bgColor rgb="00FDE7E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -276,6 +284,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00E8F5E9"/>
+          <bgColor rgb="00E8F5E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -283,6 +292,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FDE7E9"/>
+          <bgColor rgb="00FDE7E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -290,6 +300,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFF4E5"/>
+          <bgColor rgb="00FFF4E5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -297,6 +308,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00E7F0FE"/>
+          <bgColor rgb="00E7F0FE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -311,6 +323,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00A5D6A7"/>
+          <bgColor rgb="00A5D6A7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -318,6 +331,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F5B971"/>
+          <bgColor rgb="00F5B971"/>
         </patternFill>
       </fill>
     </dxf>
@@ -325,6 +339,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="003182F6"/>
+          <bgColor rgb="003182F6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -332,6 +347,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00BFDBFE"/>
+          <bgColor rgb="00BFDBFE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -339,6 +355,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFE0E6"/>
+          <bgColor rgb="00FFE0E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -346,6 +363,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F3F4F6"/>
+          <bgColor rgb="00F3F4F6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2130,62 +2148,62 @@
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="3.4" customWidth="1" min="5" max="5"/>
-    <col width="3.4" customWidth="1" min="6" max="6"/>
-    <col width="3.4" customWidth="1" min="7" max="7"/>
-    <col width="3.4" customWidth="1" min="8" max="8"/>
-    <col width="3.4" customWidth="1" min="9" max="9"/>
-    <col width="3.4" customWidth="1" min="10" max="10"/>
-    <col width="3.4" customWidth="1" min="11" max="11"/>
-    <col width="3.4" customWidth="1" min="12" max="12"/>
-    <col width="3.4" customWidth="1" min="13" max="13"/>
-    <col width="3.4" customWidth="1" min="14" max="14"/>
-    <col width="3.4" customWidth="1" min="15" max="15"/>
-    <col width="3.4" customWidth="1" min="16" max="16"/>
-    <col width="3.4" customWidth="1" min="17" max="17"/>
-    <col width="3.4" customWidth="1" min="18" max="18"/>
-    <col width="3.4" customWidth="1" min="19" max="19"/>
-    <col width="3.4" customWidth="1" min="20" max="20"/>
-    <col width="3.4" customWidth="1" min="21" max="21"/>
-    <col width="3.4" customWidth="1" min="22" max="22"/>
-    <col width="3.4" customWidth="1" min="23" max="23"/>
-    <col width="3.4" customWidth="1" min="24" max="24"/>
-    <col width="3.4" customWidth="1" min="25" max="25"/>
-    <col width="3.4" customWidth="1" min="26" max="26"/>
-    <col width="3.4" customWidth="1" min="27" max="27"/>
-    <col width="3.4" customWidth="1" min="28" max="28"/>
-    <col width="3.4" customWidth="1" min="29" max="29"/>
-    <col width="3.4" customWidth="1" min="30" max="30"/>
-    <col width="3.4" customWidth="1" min="31" max="31"/>
-    <col width="3.4" customWidth="1" min="32" max="32"/>
-    <col width="3.4" customWidth="1" min="33" max="33"/>
-    <col width="3.4" customWidth="1" min="34" max="34"/>
-    <col width="3.4" customWidth="1" min="35" max="35"/>
-    <col width="3.4" customWidth="1" min="36" max="36"/>
-    <col width="3.4" customWidth="1" min="37" max="37"/>
-    <col width="3.4" customWidth="1" min="38" max="38"/>
-    <col width="3.4" customWidth="1" min="39" max="39"/>
-    <col width="3.4" customWidth="1" min="40" max="40"/>
-    <col width="3.4" customWidth="1" min="41" max="41"/>
-    <col width="3.4" customWidth="1" min="42" max="42"/>
-    <col width="3.4" customWidth="1" min="43" max="43"/>
-    <col width="3.4" customWidth="1" min="44" max="44"/>
-    <col width="3.4" customWidth="1" min="45" max="45"/>
-    <col width="3.4" customWidth="1" min="46" max="46"/>
-    <col width="3.4" customWidth="1" min="47" max="47"/>
-    <col width="3.4" customWidth="1" min="48" max="48"/>
-    <col width="3.4" customWidth="1" min="49" max="49"/>
-    <col width="3.4" customWidth="1" min="50" max="50"/>
-    <col width="3.4" customWidth="1" min="51" max="51"/>
-    <col width="3.4" customWidth="1" min="52" max="52"/>
-    <col width="3.4" customWidth="1" min="53" max="53"/>
-    <col width="3.4" customWidth="1" min="54" max="54"/>
-    <col width="3.4" customWidth="1" min="55" max="55"/>
-    <col width="3.4" customWidth="1" min="56" max="56"/>
-    <col width="3.4" customWidth="1" min="57" max="57"/>
-    <col width="3.4" customWidth="1" min="58" max="58"/>
-    <col width="3.4" customWidth="1" min="59" max="59"/>
-    <col width="3.4" customWidth="1" min="60" max="60"/>
+    <col width="4.1" customWidth="1" min="5" max="5"/>
+    <col width="4.1" customWidth="1" min="6" max="6"/>
+    <col width="4.1" customWidth="1" min="7" max="7"/>
+    <col width="4.1" customWidth="1" min="8" max="8"/>
+    <col width="4.1" customWidth="1" min="9" max="9"/>
+    <col width="4.1" customWidth="1" min="10" max="10"/>
+    <col width="4.1" customWidth="1" min="11" max="11"/>
+    <col width="4.1" customWidth="1" min="12" max="12"/>
+    <col width="4.1" customWidth="1" min="13" max="13"/>
+    <col width="4.1" customWidth="1" min="14" max="14"/>
+    <col width="4.1" customWidth="1" min="15" max="15"/>
+    <col width="4.1" customWidth="1" min="16" max="16"/>
+    <col width="4.1" customWidth="1" min="17" max="17"/>
+    <col width="4.1" customWidth="1" min="18" max="18"/>
+    <col width="4.1" customWidth="1" min="19" max="19"/>
+    <col width="4.1" customWidth="1" min="20" max="20"/>
+    <col width="4.1" customWidth="1" min="21" max="21"/>
+    <col width="4.1" customWidth="1" min="22" max="22"/>
+    <col width="4.1" customWidth="1" min="23" max="23"/>
+    <col width="4.1" customWidth="1" min="24" max="24"/>
+    <col width="4.1" customWidth="1" min="25" max="25"/>
+    <col width="4.1" customWidth="1" min="26" max="26"/>
+    <col width="4.1" customWidth="1" min="27" max="27"/>
+    <col width="4.1" customWidth="1" min="28" max="28"/>
+    <col width="4.1" customWidth="1" min="29" max="29"/>
+    <col width="4.1" customWidth="1" min="30" max="30"/>
+    <col width="4.1" customWidth="1" min="31" max="31"/>
+    <col width="4.1" customWidth="1" min="32" max="32"/>
+    <col width="4.1" customWidth="1" min="33" max="33"/>
+    <col width="4.1" customWidth="1" min="34" max="34"/>
+    <col width="4.1" customWidth="1" min="35" max="35"/>
+    <col width="4.1" customWidth="1" min="36" max="36"/>
+    <col width="4.1" customWidth="1" min="37" max="37"/>
+    <col width="4.1" customWidth="1" min="38" max="38"/>
+    <col width="4.1" customWidth="1" min="39" max="39"/>
+    <col width="4.1" customWidth="1" min="40" max="40"/>
+    <col width="4.1" customWidth="1" min="41" max="41"/>
+    <col width="4.1" customWidth="1" min="42" max="42"/>
+    <col width="4.1" customWidth="1" min="43" max="43"/>
+    <col width="4.1" customWidth="1" min="44" max="44"/>
+    <col width="4.1" customWidth="1" min="45" max="45"/>
+    <col width="4.1" customWidth="1" min="46" max="46"/>
+    <col width="4.1" customWidth="1" min="47" max="47"/>
+    <col width="4.1" customWidth="1" min="48" max="48"/>
+    <col width="4.1" customWidth="1" min="49" max="49"/>
+    <col width="4.1" customWidth="1" min="50" max="50"/>
+    <col width="4.1" customWidth="1" min="51" max="51"/>
+    <col width="4.1" customWidth="1" min="52" max="52"/>
+    <col width="4.1" customWidth="1" min="53" max="53"/>
+    <col width="4.1" customWidth="1" min="54" max="54"/>
+    <col width="4.1" customWidth="1" min="55" max="55"/>
+    <col width="4.1" customWidth="1" min="56" max="56"/>
+    <col width="4.1" customWidth="1" min="57" max="57"/>
+    <col width="4.1" customWidth="1" min="58" max="58"/>
+    <col width="4.1" customWidth="1" min="59" max="59"/>
+    <col width="4.1" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/01-Projects/하루보고 홍보/업무 일정관리 양식 (무료배포).xlsx
+++ b/01-Projects/하루보고 홍보/업무 일정관리 양식 (무료배포).xlsx
@@ -122,54 +122,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BFDBFE"/>
-        <bgColor rgb="00BFDBFE"/>
+        <fgColor rgb="00C3D9FB"/>
+        <bgColor rgb="00C3D9FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7F0FE"/>
-        <bgColor rgb="00E7F0FE"/>
+        <fgColor rgb="002563EB"/>
+        <bgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003182F6"/>
-        <bgColor rgb="003182F6"/>
+        <fgColor rgb="00C9E7CD"/>
+        <bgColor rgb="00C9E7CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-        <bgColor rgb="00E8F5E9"/>
+        <fgColor rgb="0016A34A"/>
+        <bgColor rgb="0016A34A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A5D6A7"/>
-        <bgColor rgb="00A5D6A7"/>
+        <fgColor rgb="0094A3B8"/>
+        <bgColor rgb="0094A3B8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4E5"/>
-        <bgColor rgb="00FFF4E5"/>
+        <fgColor rgb="00FBD9A0"/>
+        <bgColor rgb="00FBD9A0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5B971"/>
-        <bgColor rgb="00F5B971"/>
+        <fgColor rgb="00F97316"/>
+        <bgColor rgb="00F97316"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE7E9"/>
-        <bgColor rgb="00FDE7E9"/>
+        <fgColor rgb="00F6C3CA"/>
+        <bgColor rgb="00F6C3CA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -182,6 +182,27 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
       <left style="hair">
@@ -224,22 +245,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,10 +306,10 @@
     <xf numFmtId="166" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="12" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -296,7 +317,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -305,32 +326,32 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E8F5E9"/>
-          <bgColor rgb="00E8F5E9"/>
+          <fgColor rgb="00C9E7CD"/>
+          <bgColor rgb="00C9E7CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FDE7E9"/>
-          <bgColor rgb="00FDE7E9"/>
+          <fgColor rgb="00F6C3CA"/>
+          <bgColor rgb="00F6C3CA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFF4E5"/>
-          <bgColor rgb="00FFF4E5"/>
+          <fgColor rgb="00FBD9A0"/>
+          <bgColor rgb="00FBD9A0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E7F0FE"/>
-          <bgColor rgb="00E7F0FE"/>
+          <fgColor rgb="00C3D9FB"/>
+          <bgColor rgb="00C3D9FB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -344,48 +365,48 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00A5D6A7"/>
-          <bgColor rgb="00A5D6A7"/>
+          <fgColor rgb="0016A34A"/>
+          <bgColor rgb="0016A34A"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F5B971"/>
-          <bgColor rgb="00F5B971"/>
+          <fgColor rgb="00F97316"/>
+          <bgColor rgb="00F97316"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="003182F6"/>
-          <bgColor rgb="003182F6"/>
+          <fgColor rgb="002563EB"/>
+          <bgColor rgb="002563EB"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00BFDBFE"/>
-          <bgColor rgb="00BFDBFE"/>
+          <fgColor rgb="0094A3B8"/>
+          <bgColor rgb="0094A3B8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFE0E6"/>
-          <bgColor rgb="00FFE0E6"/>
+          <fgColor rgb="00FBCBD5"/>
+          <bgColor rgb="00FBCBD5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F3F4F6"/>
-          <bgColor rgb="00F3F4F6"/>
+          <fgColor rgb="00E5E7EB"/>
+          <bgColor rgb="00E5E7EB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -866,7 +887,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -881,14 +902,14 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>기본 — 간트에 연파랑 막대</t>
+          <t>행이 파랑, 간트 막대는 진한 파랑 — 간트 맨 위</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -903,14 +924,14 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>행이 연파랑, 간트 막대는 진한 파랑</t>
+          <t>행·막대가 초록 — D-Day 자리에 ✔ 완료</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>예정</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -925,7 +946,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>행·막대가 초록 — D-Day 자리에 ✔ 완료</t>
+          <t>기본 — 간트에 회청색 막대</t>
         </is>
       </c>
     </row>
@@ -947,7 +968,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>행·막대가 주황</t>
+          <t>행·막대가 주황 — 간트 맨 아래</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1022,7 @@
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>· 간트차트는 진행중 → 예정 → 완료 → 보류 순으로 자동 정렬됩니다 (같은 상태끼리는 시작일 빠른 순). 일정목록의 줄 순서는 그대로 둬도 됩니다.</t>
+          <t>· 간트차트는 진행중 → 완료 → 예정 → 보류 순으로 자동 정렬됩니다 (같은 상태끼리는 시작일 빠른 순). 일정목록의 줄 순서는 그대로 둬도 됩니다.</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1099,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>⚙ 자동 계산: I열 D-Day는 자동입니다 (정렬용 계산 열은 숨김 처리 — 신경 쓰지 않아도 됩니다). 마감이 지난 미완료 일정은 자동으로 빨간 '⚠ 지연'이 되고, [간트차트]는 진행중→예정→완료→보류 순으로 자동 정렬되어 그려집니다.</t>
+          <t>⚙ 자동 계산: I열 D-Day는 자동입니다 (정렬용 계산 열은 숨김 처리 — 신경 쓰지 않아도 됩니다). 마감이 지난 미완료 일정은 자동으로 빨간 '⚠ 지연'이 되고, [간트차트]는 진행중→완료→예정→보류 순으로 자동 정렬되어 그려집니다.</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1202,7 @@
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>IF($B5="","",IF($F5="진행중",1,IF($F5="완료",3,IF($F5="보류",4,2)))*1000000000+IF($D5="",0,$D5)*10000+ROW())</f>
+        <f>IF($B5="","",IF($F5="진행중",1,IF($F5="완료",2,IF($F5="보류",4,3)))*1000000000+IF($D5="",0,$D5)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K5" s="29">
@@ -1227,7 +1248,7 @@
         <v/>
       </c>
       <c r="J6" s="29">
-        <f>IF($B6="","",IF($F6="진행중",1,IF($F6="완료",3,IF($F6="보류",4,2)))*1000000000+IF($D6="",0,$D6)*10000+ROW())</f>
+        <f>IF($B6="","",IF($F6="진행중",1,IF($F6="완료",2,IF($F6="보류",4,3)))*1000000000+IF($D6="",0,$D6)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K6" s="29">
@@ -1273,7 +1294,7 @@
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>IF($B7="","",IF($F7="진행중",1,IF($F7="완료",3,IF($F7="보류",4,2)))*1000000000+IF($D7="",0,$D7)*10000+ROW())</f>
+        <f>IF($B7="","",IF($F7="진행중",1,IF($F7="완료",2,IF($F7="보류",4,3)))*1000000000+IF($D7="",0,$D7)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K7" s="29">
@@ -1323,7 +1344,7 @@
         <v/>
       </c>
       <c r="J8" s="29">
-        <f>IF($B8="","",IF($F8="진행중",1,IF($F8="완료",3,IF($F8="보류",4,2)))*1000000000+IF($D8="",0,$D8)*10000+ROW())</f>
+        <f>IF($B8="","",IF($F8="진행중",1,IF($F8="완료",2,IF($F8="보류",4,3)))*1000000000+IF($D8="",0,$D8)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K8" s="29">
@@ -1369,7 +1390,7 @@
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>IF($B9="","",IF($F9="진행중",1,IF($F9="완료",3,IF($F9="보류",4,2)))*1000000000+IF($D9="",0,$D9)*10000+ROW())</f>
+        <f>IF($B9="","",IF($F9="진행중",1,IF($F9="완료",2,IF($F9="보류",4,3)))*1000000000+IF($D9="",0,$D9)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K9" s="29">
@@ -1415,7 +1436,7 @@
         <v/>
       </c>
       <c r="J10" s="29">
-        <f>IF($B10="","",IF($F10="진행중",1,IF($F10="완료",3,IF($F10="보류",4,2)))*1000000000+IF($D10="",0,$D10)*10000+ROW())</f>
+        <f>IF($B10="","",IF($F10="진행중",1,IF($F10="완료",2,IF($F10="보류",4,3)))*1000000000+IF($D10="",0,$D10)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K10" s="29">
@@ -1465,7 +1486,7 @@
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>IF($B11="","",IF($F11="진행중",1,IF($F11="완료",3,IF($F11="보류",4,2)))*1000000000+IF($D11="",0,$D11)*10000+ROW())</f>
+        <f>IF($B11="","",IF($F11="진행중",1,IF($F11="완료",2,IF($F11="보류",4,3)))*1000000000+IF($D11="",0,$D11)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K11" s="29">
@@ -1511,7 +1532,7 @@
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>IF($B12="","",IF($F12="진행중",1,IF($F12="완료",3,IF($F12="보류",4,2)))*1000000000+IF($D12="",0,$D12)*10000+ROW())</f>
+        <f>IF($B12="","",IF($F12="진행중",1,IF($F12="완료",2,IF($F12="보류",4,3)))*1000000000+IF($D12="",0,$D12)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K12" s="29">
@@ -1557,7 +1578,7 @@
         <v/>
       </c>
       <c r="J13" s="29">
-        <f>IF($B13="","",IF($F13="진행중",1,IF($F13="완료",3,IF($F13="보류",4,2)))*1000000000+IF($D13="",0,$D13)*10000+ROW())</f>
+        <f>IF($B13="","",IF($F13="진행중",1,IF($F13="완료",2,IF($F13="보류",4,3)))*1000000000+IF($D13="",0,$D13)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K13" s="29">
@@ -1603,7 +1624,7 @@
         <v/>
       </c>
       <c r="J14" s="29">
-        <f>IF($B14="","",IF($F14="진행중",1,IF($F14="완료",3,IF($F14="보류",4,2)))*1000000000+IF($D14="",0,$D14)*10000+ROW())</f>
+        <f>IF($B14="","",IF($F14="진행중",1,IF($F14="완료",2,IF($F14="보류",4,3)))*1000000000+IF($D14="",0,$D14)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K14" s="29">
@@ -1653,7 +1674,7 @@
         <v/>
       </c>
       <c r="J15" s="29">
-        <f>IF($B15="","",IF($F15="진행중",1,IF($F15="완료",3,IF($F15="보류",4,2)))*1000000000+IF($D15="",0,$D15)*10000+ROW())</f>
+        <f>IF($B15="","",IF($F15="진행중",1,IF($F15="완료",2,IF($F15="보류",4,3)))*1000000000+IF($D15="",0,$D15)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K15" s="29">
@@ -1699,7 +1720,7 @@
         <v/>
       </c>
       <c r="J16" s="29">
-        <f>IF($B16="","",IF($F16="진행중",1,IF($F16="완료",3,IF($F16="보류",4,2)))*1000000000+IF($D16="",0,$D16)*10000+ROW())</f>
+        <f>IF($B16="","",IF($F16="진행중",1,IF($F16="완료",2,IF($F16="보류",4,3)))*1000000000+IF($D16="",0,$D16)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K16" s="29">
@@ -1721,7 +1742,7 @@
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>IF($B17="","",IF($F17="진행중",1,IF($F17="완료",3,IF($F17="보류",4,2)))*1000000000+IF($D17="",0,$D17)*10000+ROW())</f>
+        <f>IF($B17="","",IF($F17="진행중",1,IF($F17="완료",2,IF($F17="보류",4,3)))*1000000000+IF($D17="",0,$D17)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K17" s="29">
@@ -1743,7 +1764,7 @@
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>IF($B18="","",IF($F18="진행중",1,IF($F18="완료",3,IF($F18="보류",4,2)))*1000000000+IF($D18="",0,$D18)*10000+ROW())</f>
+        <f>IF($B18="","",IF($F18="진행중",1,IF($F18="완료",2,IF($F18="보류",4,3)))*1000000000+IF($D18="",0,$D18)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K18" s="29">
@@ -1765,7 +1786,7 @@
         <v/>
       </c>
       <c r="J19" s="29">
-        <f>IF($B19="","",IF($F19="진행중",1,IF($F19="완료",3,IF($F19="보류",4,2)))*1000000000+IF($D19="",0,$D19)*10000+ROW())</f>
+        <f>IF($B19="","",IF($F19="진행중",1,IF($F19="완료",2,IF($F19="보류",4,3)))*1000000000+IF($D19="",0,$D19)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K19" s="29">
@@ -1787,7 +1808,7 @@
         <v/>
       </c>
       <c r="J20" s="29">
-        <f>IF($B20="","",IF($F20="진행중",1,IF($F20="완료",3,IF($F20="보류",4,2)))*1000000000+IF($D20="",0,$D20)*10000+ROW())</f>
+        <f>IF($B20="","",IF($F20="진행중",1,IF($F20="완료",2,IF($F20="보류",4,3)))*1000000000+IF($D20="",0,$D20)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K20" s="29">
@@ -1809,7 +1830,7 @@
         <v/>
       </c>
       <c r="J21" s="29">
-        <f>IF($B21="","",IF($F21="진행중",1,IF($F21="완료",3,IF($F21="보류",4,2)))*1000000000+IF($D21="",0,$D21)*10000+ROW())</f>
+        <f>IF($B21="","",IF($F21="진행중",1,IF($F21="완료",2,IF($F21="보류",4,3)))*1000000000+IF($D21="",0,$D21)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K21" s="29">
@@ -1831,7 +1852,7 @@
         <v/>
       </c>
       <c r="J22" s="29">
-        <f>IF($B22="","",IF($F22="진행중",1,IF($F22="완료",3,IF($F22="보류",4,2)))*1000000000+IF($D22="",0,$D22)*10000+ROW())</f>
+        <f>IF($B22="","",IF($F22="진행중",1,IF($F22="완료",2,IF($F22="보류",4,3)))*1000000000+IF($D22="",0,$D22)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K22" s="29">
@@ -1853,7 +1874,7 @@
         <v/>
       </c>
       <c r="J23" s="29">
-        <f>IF($B23="","",IF($F23="진행중",1,IF($F23="완료",3,IF($F23="보류",4,2)))*1000000000+IF($D23="",0,$D23)*10000+ROW())</f>
+        <f>IF($B23="","",IF($F23="진행중",1,IF($F23="완료",2,IF($F23="보류",4,3)))*1000000000+IF($D23="",0,$D23)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K23" s="29">
@@ -1875,7 +1896,7 @@
         <v/>
       </c>
       <c r="J24" s="29">
-        <f>IF($B24="","",IF($F24="진행중",1,IF($F24="완료",3,IF($F24="보류",4,2)))*1000000000+IF($D24="",0,$D24)*10000+ROW())</f>
+        <f>IF($B24="","",IF($F24="진행중",1,IF($F24="완료",2,IF($F24="보류",4,3)))*1000000000+IF($D24="",0,$D24)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K24" s="29">
@@ -1897,7 +1918,7 @@
         <v/>
       </c>
       <c r="J25" s="29">
-        <f>IF($B25="","",IF($F25="진행중",1,IF($F25="완료",3,IF($F25="보류",4,2)))*1000000000+IF($D25="",0,$D25)*10000+ROW())</f>
+        <f>IF($B25="","",IF($F25="진행중",1,IF($F25="완료",2,IF($F25="보류",4,3)))*1000000000+IF($D25="",0,$D25)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K25" s="29">
@@ -1919,7 +1940,7 @@
         <v/>
       </c>
       <c r="J26" s="29">
-        <f>IF($B26="","",IF($F26="진행중",1,IF($F26="완료",3,IF($F26="보류",4,2)))*1000000000+IF($D26="",0,$D26)*10000+ROW())</f>
+        <f>IF($B26="","",IF($F26="진행중",1,IF($F26="완료",2,IF($F26="보류",4,3)))*1000000000+IF($D26="",0,$D26)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K26" s="29">
@@ -1941,7 +1962,7 @@
         <v/>
       </c>
       <c r="J27" s="29">
-        <f>IF($B27="","",IF($F27="진행중",1,IF($F27="완료",3,IF($F27="보류",4,2)))*1000000000+IF($D27="",0,$D27)*10000+ROW())</f>
+        <f>IF($B27="","",IF($F27="진행중",1,IF($F27="완료",2,IF($F27="보류",4,3)))*1000000000+IF($D27="",0,$D27)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K27" s="29">
@@ -1963,7 +1984,7 @@
         <v/>
       </c>
       <c r="J28" s="29">
-        <f>IF($B28="","",IF($F28="진행중",1,IF($F28="완료",3,IF($F28="보류",4,2)))*1000000000+IF($D28="",0,$D28)*10000+ROW())</f>
+        <f>IF($B28="","",IF($F28="진행중",1,IF($F28="완료",2,IF($F28="보류",4,3)))*1000000000+IF($D28="",0,$D28)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K28" s="29">
@@ -1985,7 +2006,7 @@
         <v/>
       </c>
       <c r="J29" s="29">
-        <f>IF($B29="","",IF($F29="진행중",1,IF($F29="완료",3,IF($F29="보류",4,2)))*1000000000+IF($D29="",0,$D29)*10000+ROW())</f>
+        <f>IF($B29="","",IF($F29="진행중",1,IF($F29="완료",2,IF($F29="보류",4,3)))*1000000000+IF($D29="",0,$D29)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K29" s="29">
@@ -2007,7 +2028,7 @@
         <v/>
       </c>
       <c r="J30" s="29">
-        <f>IF($B30="","",IF($F30="진행중",1,IF($F30="완료",3,IF($F30="보류",4,2)))*1000000000+IF($D30="",0,$D30)*10000+ROW())</f>
+        <f>IF($B30="","",IF($F30="진행중",1,IF($F30="완료",2,IF($F30="보류",4,3)))*1000000000+IF($D30="",0,$D30)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K30" s="29">
@@ -2029,7 +2050,7 @@
         <v/>
       </c>
       <c r="J31" s="29">
-        <f>IF($B31="","",IF($F31="진행중",1,IF($F31="완료",3,IF($F31="보류",4,2)))*1000000000+IF($D31="",0,$D31)*10000+ROW())</f>
+        <f>IF($B31="","",IF($F31="진행중",1,IF($F31="완료",2,IF($F31="보류",4,3)))*1000000000+IF($D31="",0,$D31)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K31" s="29">
@@ -2051,7 +2072,7 @@
         <v/>
       </c>
       <c r="J32" s="29">
-        <f>IF($B32="","",IF($F32="진행중",1,IF($F32="완료",3,IF($F32="보류",4,2)))*1000000000+IF($D32="",0,$D32)*10000+ROW())</f>
+        <f>IF($B32="","",IF($F32="진행중",1,IF($F32="완료",2,IF($F32="보류",4,3)))*1000000000+IF($D32="",0,$D32)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K32" s="29">
@@ -2073,7 +2094,7 @@
         <v/>
       </c>
       <c r="J33" s="29">
-        <f>IF($B33="","",IF($F33="진행중",1,IF($F33="완료",3,IF($F33="보류",4,2)))*1000000000+IF($D33="",0,$D33)*10000+ROW())</f>
+        <f>IF($B33="","",IF($F33="진행중",1,IF($F33="완료",2,IF($F33="보류",4,3)))*1000000000+IF($D33="",0,$D33)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K33" s="29">
@@ -2095,7 +2116,7 @@
         <v/>
       </c>
       <c r="J34" s="29">
-        <f>IF($B34="","",IF($F34="진행중",1,IF($F34="완료",3,IF($F34="보류",4,2)))*1000000000+IF($D34="",0,$D34)*10000+ROW())</f>
+        <f>IF($B34="","",IF($F34="진행중",1,IF($F34="완료",2,IF($F34="보류",4,3)))*1000000000+IF($D34="",0,$D34)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K34" s="29">
@@ -2117,7 +2138,7 @@
         <v/>
       </c>
       <c r="J35" s="29">
-        <f>IF($B35="","",IF($F35="진행중",1,IF($F35="완료",3,IF($F35="보류",4,2)))*1000000000+IF($D35="",0,$D35)*10000+ROW())</f>
+        <f>IF($B35="","",IF($F35="진행중",1,IF($F35="완료",2,IF($F35="보류",4,3)))*1000000000+IF($D35="",0,$D35)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K35" s="29">
@@ -2139,7 +2160,7 @@
         <v/>
       </c>
       <c r="J36" s="29">
-        <f>IF($B36="","",IF($F36="진행중",1,IF($F36="완료",3,IF($F36="보류",4,2)))*1000000000+IF($D36="",0,$D36)*10000+ROW())</f>
+        <f>IF($B36="","",IF($F36="진행중",1,IF($F36="완료",2,IF($F36="보류",4,3)))*1000000000+IF($D36="",0,$D36)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K36" s="29">
@@ -2161,7 +2182,7 @@
         <v/>
       </c>
       <c r="J37" s="29">
-        <f>IF($B37="","",IF($F37="진행중",1,IF($F37="완료",3,IF($F37="보류",4,2)))*1000000000+IF($D37="",0,$D37)*10000+ROW())</f>
+        <f>IF($B37="","",IF($F37="진행중",1,IF($F37="완료",2,IF($F37="보류",4,3)))*1000000000+IF($D37="",0,$D37)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K37" s="29">
@@ -2183,7 +2204,7 @@
         <v/>
       </c>
       <c r="J38" s="29">
-        <f>IF($B38="","",IF($F38="진행중",1,IF($F38="완료",3,IF($F38="보류",4,2)))*1000000000+IF($D38="",0,$D38)*10000+ROW())</f>
+        <f>IF($B38="","",IF($F38="진행중",1,IF($F38="완료",2,IF($F38="보류",4,3)))*1000000000+IF($D38="",0,$D38)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K38" s="29">
@@ -2205,7 +2226,7 @@
         <v/>
       </c>
       <c r="J39" s="29">
-        <f>IF($B39="","",IF($F39="진행중",1,IF($F39="완료",3,IF($F39="보류",4,2)))*1000000000+IF($D39="",0,$D39)*10000+ROW())</f>
+        <f>IF($B39="","",IF($F39="진행중",1,IF($F39="완료",2,IF($F39="보류",4,3)))*1000000000+IF($D39="",0,$D39)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K39" s="29">
@@ -2227,7 +2248,7 @@
         <v/>
       </c>
       <c r="J40" s="29">
-        <f>IF($B40="","",IF($F40="진행중",1,IF($F40="완료",3,IF($F40="보류",4,2)))*1000000000+IF($D40="",0,$D40)*10000+ROW())</f>
+        <f>IF($B40="","",IF($F40="진행중",1,IF($F40="완료",2,IF($F40="보류",4,3)))*1000000000+IF($D40="",0,$D40)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K40" s="29">
@@ -2249,7 +2270,7 @@
         <v/>
       </c>
       <c r="J41" s="29">
-        <f>IF($B41="","",IF($F41="진행중",1,IF($F41="완료",3,IF($F41="보류",4,2)))*1000000000+IF($D41="",0,$D41)*10000+ROW())</f>
+        <f>IF($B41="","",IF($F41="진행중",1,IF($F41="완료",2,IF($F41="보류",4,3)))*1000000000+IF($D41="",0,$D41)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K41" s="29">
@@ -2271,7 +2292,7 @@
         <v/>
       </c>
       <c r="J42" s="29">
-        <f>IF($B42="","",IF($F42="진행중",1,IF($F42="완료",3,IF($F42="보류",4,2)))*1000000000+IF($D42="",0,$D42)*10000+ROW())</f>
+        <f>IF($B42="","",IF($F42="진행중",1,IF($F42="완료",2,IF($F42="보류",4,3)))*1000000000+IF($D42="",0,$D42)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K42" s="29">
@@ -2293,7 +2314,7 @@
         <v/>
       </c>
       <c r="J43" s="29">
-        <f>IF($B43="","",IF($F43="진행중",1,IF($F43="완료",3,IF($F43="보류",4,2)))*1000000000+IF($D43="",0,$D43)*10000+ROW())</f>
+        <f>IF($B43="","",IF($F43="진행중",1,IF($F43="완료",2,IF($F43="보류",4,3)))*1000000000+IF($D43="",0,$D43)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K43" s="29">
@@ -2315,7 +2336,7 @@
         <v/>
       </c>
       <c r="J44" s="29">
-        <f>IF($B44="","",IF($F44="진행중",1,IF($F44="완료",3,IF($F44="보류",4,2)))*1000000000+IF($D44="",0,$D44)*10000+ROW())</f>
+        <f>IF($B44="","",IF($F44="진행중",1,IF($F44="완료",2,IF($F44="보류",4,3)))*1000000000+IF($D44="",0,$D44)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K44" s="29">
@@ -2337,7 +2358,7 @@
         <v/>
       </c>
       <c r="J45" s="29">
-        <f>IF($B45="","",IF($F45="진행중",1,IF($F45="완료",3,IF($F45="보류",4,2)))*1000000000+IF($D45="",0,$D45)*10000+ROW())</f>
+        <f>IF($B45="","",IF($F45="진행중",1,IF($F45="완료",2,IF($F45="보류",4,3)))*1000000000+IF($D45="",0,$D45)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K45" s="29">
@@ -2359,7 +2380,7 @@
         <v/>
       </c>
       <c r="J46" s="29">
-        <f>IF($B46="","",IF($F46="진행중",1,IF($F46="완료",3,IF($F46="보류",4,2)))*1000000000+IF($D46="",0,$D46)*10000+ROW())</f>
+        <f>IF($B46="","",IF($F46="진행중",1,IF($F46="완료",2,IF($F46="보류",4,3)))*1000000000+IF($D46="",0,$D46)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K46" s="29">
@@ -2381,7 +2402,7 @@
         <v/>
       </c>
       <c r="J47" s="29">
-        <f>IF($B47="","",IF($F47="진행중",1,IF($F47="완료",3,IF($F47="보류",4,2)))*1000000000+IF($D47="",0,$D47)*10000+ROW())</f>
+        <f>IF($B47="","",IF($F47="진행중",1,IF($F47="완료",2,IF($F47="보류",4,3)))*1000000000+IF($D47="",0,$D47)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K47" s="29">
@@ -2403,7 +2424,7 @@
         <v/>
       </c>
       <c r="J48" s="29">
-        <f>IF($B48="","",IF($F48="진행중",1,IF($F48="완료",3,IF($F48="보류",4,2)))*1000000000+IF($D48="",0,$D48)*10000+ROW())</f>
+        <f>IF($B48="","",IF($F48="진행중",1,IF($F48="완료",2,IF($F48="보류",4,3)))*1000000000+IF($D48="",0,$D48)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K48" s="29">
@@ -2425,7 +2446,7 @@
         <v/>
       </c>
       <c r="J49" s="29">
-        <f>IF($B49="","",IF($F49="진행중",1,IF($F49="완료",3,IF($F49="보류",4,2)))*1000000000+IF($D49="",0,$D49)*10000+ROW())</f>
+        <f>IF($B49="","",IF($F49="진행중",1,IF($F49="완료",2,IF($F49="보류",4,3)))*1000000000+IF($D49="",0,$D49)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K49" s="29">
@@ -2447,7 +2468,7 @@
         <v/>
       </c>
       <c r="J50" s="29">
-        <f>IF($B50="","",IF($F50="진행중",1,IF($F50="완료",3,IF($F50="보류",4,2)))*1000000000+IF($D50="",0,$D50)*10000+ROW())</f>
+        <f>IF($B50="","",IF($F50="진행중",1,IF($F50="완료",2,IF($F50="보류",4,3)))*1000000000+IF($D50="",0,$D50)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K50" s="29">
@@ -2469,7 +2490,7 @@
         <v/>
       </c>
       <c r="J51" s="29">
-        <f>IF($B51="","",IF($F51="진행중",1,IF($F51="완료",3,IF($F51="보류",4,2)))*1000000000+IF($D51="",0,$D51)*10000+ROW())</f>
+        <f>IF($B51="","",IF($F51="진행중",1,IF($F51="완료",2,IF($F51="보류",4,3)))*1000000000+IF($D51="",0,$D51)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K51" s="29">
@@ -2491,7 +2512,7 @@
         <v/>
       </c>
       <c r="J52" s="29">
-        <f>IF($B52="","",IF($F52="진행중",1,IF($F52="완료",3,IF($F52="보류",4,2)))*1000000000+IF($D52="",0,$D52)*10000+ROW())</f>
+        <f>IF($B52="","",IF($F52="진행중",1,IF($F52="완료",2,IF($F52="보류",4,3)))*1000000000+IF($D52="",0,$D52)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K52" s="29">
@@ -2513,7 +2534,7 @@
         <v/>
       </c>
       <c r="J53" s="29">
-        <f>IF($B53="","",IF($F53="진행중",1,IF($F53="완료",3,IF($F53="보류",4,2)))*1000000000+IF($D53="",0,$D53)*10000+ROW())</f>
+        <f>IF($B53="","",IF($F53="진행중",1,IF($F53="완료",2,IF($F53="보류",4,3)))*1000000000+IF($D53="",0,$D53)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K53" s="29">
@@ -2535,7 +2556,7 @@
         <v/>
       </c>
       <c r="J54" s="29">
-        <f>IF($B54="","",IF($F54="진행중",1,IF($F54="완료",3,IF($F54="보류",4,2)))*1000000000+IF($D54="",0,$D54)*10000+ROW())</f>
+        <f>IF($B54="","",IF($F54="진행중",1,IF($F54="완료",2,IF($F54="보류",4,3)))*1000000000+IF($D54="",0,$D54)*10000+ROW())</f>
         <v/>
       </c>
       <c r="K54" s="29">
@@ -2665,7 +2686,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>⚙ 자동 계산: 일정목록을 진행중→예정→완료→보류 순으로 자동 정렬해(같은 상태는 시작일순) 상태별 색 막대를 그립니다. 회색 세로줄=주말, 분홍 세로줄=오늘. 완료=초록 · 진행중=파랑 · 보류=주황 · 예정=연파랑. 정렬용 계산 열은 숨김 처리되어 있습니다.</t>
+          <t>⚙ 자동 계산: 일정목록을 진행중→완료→예정→보류 순으로 자동 정렬해(같은 상태는 시작일순) 상태별 색 막대를 그립니다. 회색 세로줄=주말, 분홍 세로줄=오늘. 진행중=파랑 · 완료=초록 · 예정=회청 · 보류=주황. 정렬용 계산 열은 숨김 처리되어 있습니다.</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2699,8 @@
       <c r="B4" s="34" t="n">
         <v>46286</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>◀ 이 날부터 8주 표시 (월요일 권장)</t>
         </is>
@@ -6836,6 +6858,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
   <conditionalFormatting sqref="E6:BH55">
     <cfRule type="expression" priority="1" dxfId="5" stopIfTrue="1">
       <formula>AND(E$5&lt;&gt;"",$B6&lt;&gt;"",E$5&gt;=$B6,E$5&lt;=$C6,$D6="완료")</formula>
